--- a/yolo-seg__ANN/B7_正規化摘要.xlsx
+++ b/yolo-seg__ANN/B7_正規化摘要.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="mask幾何_三種尺度" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="mask幾何_長邊正規化_分組" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="長邊正規化_前後" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="三種尺度_各seed" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="三種尺度_跨seed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="mask幾何_長邊正規化_seed2_分組" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,76 +416,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>尺度</t>
+          <t>方法</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>px/mm CV</t>
+          <t>train_seed</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>X–Y r</t>
+          <t>CV_未正規化</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CV_正規化後</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>r_未正規化</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>r_正規化後</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>不正規化</t>
+          <t>mask幾何</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.081</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.193</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>長邊</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.109</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>短邊</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.106</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>對角線</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.108</v>
+        <v>0.08110000000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2113</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1103</v>
       </c>
     </row>
   </sheetData>
@@ -497,6 +484,263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>train_seed</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>尺度</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>px/mm CV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>X–Y r</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>不正規化</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.211</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>長邊</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>短邊</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>對角線</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>px/mm CV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>X–Y r</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>尺度</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>不正規化</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>長邊</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>短邊</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>對角線</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="E1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -532,7 +776,7 @@
         <v>38</v>
       </c>
       <c r="C2" t="n">
-        <v>24.305</v>
+        <v>24.233</v>
       </c>
       <c r="D2" t="n">
         <v>0.08</v>
@@ -548,7 +792,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>12.131</v>
+        <v>12.059</v>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
@@ -564,10 +808,10 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>23.097</v>
+        <v>22.95</v>
       </c>
       <c r="D4" t="n">
-        <v>0.054</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="5">
@@ -580,10 +824,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>15.522</v>
+        <v>15.759</v>
       </c>
       <c r="D5" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="6">
@@ -596,7 +840,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>33.76</v>
+        <v>33.372</v>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
@@ -610,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>39.272</v>
+        <v>38.894</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
@@ -624,7 +868,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>37.489</v>
+        <v>37.191</v>
       </c>
       <c r="D8" t="inlineStr"/>
     </row>
@@ -638,7 +882,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>33.636</v>
+        <v>33.554</v>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
@@ -652,7 +896,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>32.953</v>
+        <v>32.938</v>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
@@ -666,7 +910,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>36.091</v>
+        <v>35.41</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
@@ -680,7 +924,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>39.189</v>
+        <v>39.209</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
